--- a/artfynd/A 53357-2025 artfynd.xlsx
+++ b/artfynd/A 53357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>399258</v>
+        <v>390932</v>
       </c>
       <c r="B2" t="n">
-        <v>81971</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -708,34 +703,20 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Adelsö-Sättra naturreservat, Upl</t>
+          <t>300 M SO NYBYGGET (10I8b01), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654621.1743104658</v>
+        <v>654673</v>
       </c>
       <c r="R2" t="n">
-        <v>6592078.610208509</v>
+        <v>6592126</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-04-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-04-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>väldigt rik lokal</t>
+          <t>100881011 / SAR GLOU / Enstaka-sparsam (1)  / OBJ.AREA:0,5 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,53 +762,38 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>hög luftfuktighet</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>färska ex, runt äldre granar i tunn mossamatta</t>
+          <t>Sandbarrskog /</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Möllegård</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Möllegård</t>
+          <t>Stefan Eklund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>ÅGP inventering</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7246594</v>
+        <v>399258</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -860,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -868,20 +824,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybygget, Lennartsnäs, Upl</t>
+          <t>Adelsö-Sättra naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654658.2623984981</v>
+        <v>654621</v>
       </c>
       <c r="R3" t="n">
-        <v>6592107.11946121</v>
+        <v>6592079</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,27 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-04-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-02-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-04-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-02-28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>320m SO om Nybygget ganska nära ett hygge. På väggmossa i ganska gles granskog, snart avverkningsbar.</t>
+          <t>väldigt rik lokal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,38 +884,51 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>hög luftfuktighet</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>färska ex, runt äldre granar i tunn mossamatta</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Åkerberg</t>
+          <t>Johan Möllegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Åkerberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Johan Möllegård</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>ÅGP inventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>390932</v>
+        <v>7246594</v>
       </c>
       <c r="B4" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -986,20 +949,30 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>300 M SO NYBYGGET (10I8b01), Upl</t>
+          <t>Nybygget, Lennartsnäs, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654672.7888446902</v>
+        <v>654658</v>
       </c>
       <c r="R4" t="n">
-        <v>6592126.046816764</v>
+        <v>6592107</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,27 +996,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1998-04-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1998-04-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>100881011 / SAR GLOU / Enstaka-sparsam (1)  / OBJ.AREA:0,5 ha</t>
+          <t>320m SO om Nybygget ganska nära ett hygge. På väggmossa i ganska gles granskog, snart avverkningsbar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,30 +1015,130 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Sandbarrskog /</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Michael Åkerberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Eklund</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
-        </is>
-      </c>
+          <t>Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>52953354</v>
+      </c>
+      <c r="B5" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tunaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>654671</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6592032</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kungsängen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Möllegård</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Möllegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
